--- a/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N43_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T7503_W0058F0002T0006Z000C1N43_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>39.68869951220842</v>
+        <v>6.449413670733867</v>
       </c>
       <c r="D2" t="n">
-        <v>33.2699797949376</v>
+        <v>5.40637171667736</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
